--- a/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_2025-10-24.xlsx
+++ b/WorkBot/refactor/data/orders/FingerLakes Farms/FingerLakes Farms_Downtown_2025-10-24.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47.50</t>
+          <t>23.75</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18.50</t>
+          <t>9.25</t>
         </is>
       </c>
     </row>
